--- a/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_calibration_due_register_2024.xlsx
+++ b/data/canary/valcan_pack_2026-04-12/_VALCAN_2026/20_LOGISTICS/valcanary_calibration_due_register_2024.xlsx
@@ -594,7 +594,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VALSITE-DELTA</t>
+          <t>Site: Validation Delta Site</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>VALSITE-ECHO</t>
+          <t>Site: Validation Echo Site</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>VALSITE-ALPHA</t>
+          <t>Site: Validation Alpha Site</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -762,7 +762,6 @@
           <t>2024-09-15</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>OVERDUE</t>
@@ -782,7 +781,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>VALSITE-BRAVO</t>
+          <t>Site: Validation Bravo Site</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -790,7 +789,6 @@
           <t>2024-10-20</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>OVERDUE</t>
@@ -810,7 +808,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>VALSITE-CHARLIE</t>
+          <t>Site: Validation Charlie Site</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -818,7 +816,6 @@
           <t>2024-11-30</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>OVERDUE</t>
